--- a/artfynd/A 46794-2025 artfynd.xlsx
+++ b/artfynd/A 46794-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3787740</v>
+        <v>65809277</v>
       </c>
       <c r="B2" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>100572</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Mindre ekbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Cerambyx scopolii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Fuessly, 1775</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebbeskogsgatan., Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622677.0380769849</v>
+        <v>622596</v>
       </c>
       <c r="R2" t="n">
-        <v>6356276.251725151</v>
+        <v>6356159</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-08-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-08-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>stockupplag i blandlövsskog. Ett litet stockupplag i skogskanten mest ek men lite asp. Kom flygandes.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,33 +778,33 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>Ek-hasselskog med inslag av lind, asp och barr. Örtrik.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Ekstock.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2156822</v>
+        <v>2156821</v>
       </c>
       <c r="B3" t="n">
-        <v>107996</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622677.0380769849</v>
+        <v>622629</v>
       </c>
       <c r="R3" t="n">
-        <v>6356276.251725151</v>
+        <v>6356226</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +869,9 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,19 +899,18 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3787739</v>
+        <v>2156822</v>
       </c>
       <c r="B4" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,39 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>219677</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622639.0609641478</v>
+        <v>622677</v>
       </c>
       <c r="R4" t="n">
-        <v>6356279.435200224</v>
+        <v>6356276</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,19 +975,9 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,41 +1005,40 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2279126</v>
+        <v>2220841</v>
       </c>
       <c r="B5" t="n">
-        <v>96224</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219769</v>
+        <v>219711</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622660.5193148615</v>
+        <v>622730</v>
       </c>
       <c r="R5" t="n">
-        <v>6356267.655330306</v>
+        <v>6356290</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,19 +1086,9 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,19 +1116,18 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2156821</v>
+        <v>2279123</v>
       </c>
       <c r="B6" t="n">
-        <v>107996</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,34 +1135,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219677</v>
+        <v>219769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Lindresrvatet norr, Öl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622628.7493565354</v>
+        <v>622743</v>
       </c>
       <c r="R6" t="n">
-        <v>6356226.195589232</v>
+        <v>6356252</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,21 +1197,11 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1252,7 +1213,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1266,19 +1227,18 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5053637</v>
+        <v>2279126</v>
       </c>
       <c r="B7" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,34 +1246,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>219769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622660.5193148615</v>
+        <v>622661</v>
       </c>
       <c r="R7" t="n">
-        <v>6356267.655330306</v>
+        <v>6356268</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1343,19 +1308,9 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,7 +1338,445 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3787736</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lindresrvatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>622743</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6356252</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3787739</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>622639</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6356279</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3787740</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>622677</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6356276</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5053637</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>622661</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6356268</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46794-2025 artfynd.xlsx
+++ b/artfynd/A 46794-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65809277</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2156821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2156822</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2220841</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2279123</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2279126</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787736</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787739</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787740</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,8 +1827,25 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5053637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>